--- a/scripts/data/output/MixedLM_Model_results_Family_line_macroarea.xlsx
+++ b/scripts/data/output/MixedLM_Model_results_Family_line_macroarea.xlsx
@@ -655,17 +655,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.694</t>
+          <t>3.884</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9288137291910952 &gt; 0.0</t>
+          <t>0.9844189406661983 &gt; 0.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -710,57 +710,57 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.558</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1.0 &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.298</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.093</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3.192</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>0.001</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>1.0 &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.281</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.094</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2.996</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.003</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -797,112 +797,112 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.092</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.906</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.0 &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.321</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>0.086</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.668</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3.718</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1633</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1633</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>1.0 &gt; 0.0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.283</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.081</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>3.478</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.085</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3.412</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.001</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>1.0 &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.255</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.080</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>3.174</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.002</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.360</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>2.936</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.110</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4.045</t>
+          <t>4.042</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.957</t>
+          <t>3.994</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>0.502</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.547</t>
+          <t>4.643</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5.318</t>
+          <t>5.435</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>0.510</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.998</t>
+          <t>5.145</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">

--- a/scripts/data/output/MixedLM_Model_results_Family_line_macroarea.xlsx
+++ b/scripts/data/output/MixedLM_Model_results_Family_line_macroarea.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.884</t>
+          <t>3.891</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3.558</t>
+          <t>3.565</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.906</t>
+          <t>3.915</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3.718</t>
+          <t>3.728</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.412</t>
+          <t>3.421</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -939,17 +939,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.360</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>2.932</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8772306129794691 &gt; 0.0</t>
+          <t>0.892459313089637 &gt; 0.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4.042</t>
+          <t>4.038</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.994</t>
+          <t>3.991</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.643</t>
+          <t>4.646</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.751245840468492 &gt; 0.0</t>
+          <t>0.7481788775469461 &gt; 0.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5.435</t>
+          <t>5.438</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.751245840468492 &gt; 0.0</t>
+          <t>0.7481788775469461 &gt; 0.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.510</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5.145</t>
+          <t>5.149</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
